--- a/output/北塩原村_サービス見込量算定.xlsx
+++ b/output/北塩原村_サービス見込量算定.xlsx
@@ -906,7 +906,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>村に該当者数を確認する（M-5）</t>
+          <t>村に該当者数を確認する（Ｍ-5）</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>村に該当者数を確認する（M-5）</t>
+          <t>村に該当者数を確認する（Ｍ-5）</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>医療的ケア児1人が18歳に達した後は医療的ケア者として内数に計上する。年齢を村に確認する（M-6）</t>
+          <t>医療的ケア児1人が18歳に達した後は医療的ケア者として内数に計上する。年齢を村に確認する（Ｍ-6）</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>村に該当者数を確認する（M-5）</t>
+          <t>村に該当者数を確認する（Ｍ-5）</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>村に該当者数を確認する（M-5）</t>
+          <t>村に該当者数を確認する（Ｍ-5）</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>医療的ケア児1人が18歳に達した後は医療的ケア者として内数に計上する。年齢を村に確認する（M-6）</t>
+          <t>医療的ケア児1人が18歳に達した後は医療的ケア者として内数に計上する。年齢を村に確認する（Ｍ-6）</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>村に該当者数を確認する（M-5）</t>
+          <t>村に該当者数を確認する（Ｍ-5）</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>村に該当者数を確認する（M-5）</t>
+          <t>村に該当者数を確認する（Ｍ-5）</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>医療的ケア児1人が18歳に達した後は医療的ケア者として内数に計上する。年齢を村に確認する（M-6）</t>
+          <t>医療的ケア児1人が18歳に達した後は医療的ケア者として内数に計上する。年齢を村に確認する（Ｍ-6）</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>村に該当者数を確認する（M-5）</t>
+          <t>村に該当者数を確認する（Ｍ-5）</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>村に該当者数を確認する（M-5）</t>
+          <t>村に該当者数を確認する（Ｍ-5）</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>医療的ケア児1人が18歳に達した後は医療的ケア者として内数に計上する。年齢を村に確認する（M-6）</t>
+          <t>医療的ケア児1人が18歳に達した後は医療的ケア者として内数に計上する。年齢を村に確認する（Ｍ-6）</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>M-1</t>
+          <t>Ｍ-1</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -1345,7 +1345,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>M-2</t>
+          <t>Ｍ-2</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -1377,7 +1377,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>M-3</t>
+          <t>Ｍ-3</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -1409,7 +1409,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>M-4</t>
+          <t>Ｍ-4</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>M-5</t>
+          <t>Ｍ-5</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>M-6</t>
+          <t>Ｍ-6</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -1505,7 +1505,7 @@
     <row r="12" ht="38" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>M-7</t>
+          <t>Ｍ-7</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -1537,7 +1537,7 @@
     <row r="13" ht="38" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>M-8</t>
+          <t>Ｍ-8</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -4935,7 +4935,7 @@
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>国庫負担基準額を超える分は村の負担になります。本村は共同生活援助・施設入所支援の利用者の割合が高く、国庫負担基準額との関係を村の決算で確認する必要があります（確認事項 M-7）。地域生活支援事業（国1/2以内・県1/4以内の統合補助金）と村単独事業はこの表に含みません。</t>
+          <t>国庫負担基準額を超える分は村の負担になります。本村は共同生活援助・施設入所支援の利用者の割合が高く、国庫負担基準額との関係を村の決算で確認する必要があります（確認事項 Ｍ-7）。地域生活支援事業（国1/2以内・県1/4以内の統合補助金）と村単独事業はこの表に含みません。</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>村への確認（M-4）。実在しなければ0、実在すれば単価とともに計上する</t>
+          <t>村への確認（Ｍ-4）。実在しなければ0、実在すれば単価とともに計上する</t>
         </is>
       </c>
       <c r="F9" s="27" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>村への確認（M-1）。就学による移行であれば妥当、転出や利用中止であれば新規の発生を見込む必要がある</t>
+          <t>村への確認（Ｍ-1）。就学による移行であれば妥当、転出や利用中止であれば新規の発生を見込む必要がある</t>
         </is>
       </c>
       <c r="F11" s="27" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>村への確認（M-5・M-6）</t>
+          <t>村への確認（Ｍ-5・Ｍ-6）</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>就労選択支援は令和8年度の実績、Ａ型は村への確認（M-4）</t>
+          <t>就労選択支援は令和8年度の実績、Ａ型は村への確認（Ｍ-4）</t>
         </is>
       </c>
       <c r="F15" s="27" t="inlineStr">
